--- a/Hardware-Designing/_Design Files v4.5/Project Outputs for Audio_Meter_V4.5/Audio_Meter_V4.5.xlsx
+++ b/Hardware-Designing/_Design Files v4.5/Project Outputs for Audio_Meter_V4.5/Audio_Meter_V4.5.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iftik\Desktop\Sid\RoomMonitor-Eduardo-sidra\Hardware-Designing\_Design Files v4.5\Project Outputs for Audio_Meter_V4.5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\RoomMonitor-Eduardo\Hardware-Designing\_Design Files v4.5\Project Outputs for Audio_Meter_V4.5\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="202">
   <si>
     <t>Comment</t>
   </si>
@@ -59,7 +59,7 @@
     <t>CAP CER 0.1UF 50V Y5V 0603</t>
   </si>
   <si>
-    <t>C1, C2, C3, C4, C7, C10, C11, C13, C17, C19, C22, C25, C26, C28, C38, C76, C79, C80, C82, C85</t>
+    <t>C1, C2, C3, C4, C7, C10, C11, C13, C17, C19, C22, C25, C26, C28, C38, C76, C79, C80, C82, C85, C#3, C#5</t>
   </si>
   <si>
     <t>Cap0603</t>
@@ -107,7 +107,7 @@
     <t>CAP CER 1UF 16V X7R 0805</t>
   </si>
   <si>
-    <t>C16, C18, C27, C29, C35, C78</t>
+    <t>C16, C18, C27, C29, C35, C78, C#4</t>
   </si>
   <si>
     <t>Cap0805</t>
@@ -275,15 +275,6 @@
     <t>ON Semiconductor</t>
   </si>
   <si>
-    <t>DMP2045U-7</t>
-  </si>
-  <si>
-    <t>MOSFET P-CHAN 24V SOT23</t>
-  </si>
-  <si>
-    <t>Q7</t>
-  </si>
-  <si>
     <t>PMV65XP,215</t>
   </si>
   <si>
@@ -320,7 +311,7 @@
     <t>RES SMD 10K OHM 5% 1/2W 0805</t>
   </si>
   <si>
-    <t>R1#, R2, R3, R4, R4#, R5, R8, R10, R12, R14, R24, R29, R35, R36, R37, R38, R40, R43, R56, R57, R83, RC1, RC2, RC3</t>
+    <t>R1#, R2, R3, R4, R4#, R5, R8, R10, R12, R14, R24, R29, R35, R36, R37, R38, R40, R43, R55, R56, R57, R83, RC1, RC2, RC3</t>
   </si>
   <si>
     <t>ERJ-P06J103V</t>
@@ -464,15 +455,6 @@
     <t>Vishay Dale Thin Film</t>
   </si>
   <si>
-    <t>RES SMD 10K OHM 5% 1/16W 0402</t>
-  </si>
-  <si>
-    <t>R55</t>
-  </si>
-  <si>
-    <t>RC0402JR-0710KL</t>
-  </si>
-  <si>
     <t>Switch</t>
   </si>
   <si>
@@ -639,6 +621,18 @@
   </si>
   <si>
     <t>STMicroelectronics</t>
+  </si>
+  <si>
+    <t>MIC2004-0.5YM5-TR</t>
+  </si>
+  <si>
+    <t>IC PWR SWITCH P-CHAN 1:1 SOT23-5</t>
+  </si>
+  <si>
+    <t>U15</t>
+  </si>
+  <si>
+    <t>Microchip</t>
   </si>
 </sst>
 </file>
@@ -990,7 +984,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="16.5703125" customWidth="1"/>
@@ -1024,7 +1018,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -1041,7 +1035,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
@@ -1102,7 +1096,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>24</v>
       </c>
@@ -1119,7 +1113,7 @@
         <v>28</v>
       </c>
       <c r="F5" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>29</v>
@@ -1450,7 +1444,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>82</v>
@@ -1458,201 +1452,201 @@
     </row>
     <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F19" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="E20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" s="4">
+        <v>25</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F20" s="4">
-        <v>2</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="H20" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F21" s="4">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F22" s="4">
         <v>1</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F23" s="4">
         <v>1</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F24" s="4">
         <v>1</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F25" s="4">
         <v>1</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>116</v>
+        <v>13</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F26" s="4">
         <v>1</v>
@@ -1661,24 +1655,24 @@
         <v>13</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F27" s="4">
         <v>1</v>
@@ -1687,125 +1681,125 @@
         <v>13</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="E28" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F28" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F29" s="4">
         <v>2</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>92</v>
+        <v>139</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F30" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F31" s="4">
         <v>1</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>147</v>
@@ -1814,21 +1808,21 @@
         <v>1</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>151</v>
@@ -1840,348 +1834,322 @@
         <v>1</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="F34" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>157</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F35" s="4">
         <v>1</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="F36" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="E37" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F37" s="4">
         <v>1</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>170</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F38" s="4">
         <v>1</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="E39" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F39" s="4">
         <v>1</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F40" s="4">
         <v>1</v>
       </c>
       <c r="G40" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F41" s="4">
         <v>1</v>
       </c>
       <c r="G41" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C42" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="F42" s="4">
         <v>1</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="F43" s="4">
         <v>1</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="E44" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F44" s="4">
         <v>1</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="F45" s="4">
         <v>1</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="F46" s="4">
-        <v>1</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
